--- a/public/Master Fabrication.xlsx
+++ b/public/Master Fabrication.xlsx
@@ -56,10 +56,10 @@
     <t>ORM000000004</t>
   </si>
   <si>
-    <t>FAB000000001</t>
-  </si>
-  <si>
-    <t>FML000000001</t>
+    <t>FAB000000002</t>
+  </si>
+  <si>
+    <t>FBM000000001</t>
   </si>
   <si>
     <t>SOLID:
